--- a/data/input/portfolio.xlsx
+++ b/data/input/portfolio.xlsx
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G825"/>
+  <dimension ref="A1:G833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21607,6 +21607,206 @@
       </c>
       <c r="G825" t="n">
         <v>8853200</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>ACB</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="D826" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="E826" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="F826" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G826" t="n">
+        <v>9239200</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>CTD</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="D827" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="E827" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F827" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G827" t="n">
+        <v>157100</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>DGC</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="D828" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="E828" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F828" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G828" t="n">
+        <v>957500</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>FPT</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="D829" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E829" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="F829" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="G829" t="n">
+        <v>6626700</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D830" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E830" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="F830" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G830" t="n">
+        <v>17574100</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>KBC</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="D831" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="E831" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="F831" t="n">
+        <v>26</v>
+      </c>
+      <c r="G831" t="n">
+        <v>1497500</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>MBB</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="D832" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="E832" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F832" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="G832" t="n">
+        <v>16498200</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>VCI</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D833" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="E833" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="F833" t="n">
+        <v>20</v>
+      </c>
+      <c r="G833" t="n">
+        <v>18343400</v>
       </c>
     </row>
   </sheetData>
